--- a/build/Namibia_2026_Kosten.xlsx
+++ b/build/Namibia_2026_Kosten.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 Bezahlt'!$A$4:$L$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02 Laufend'!$A$4:$N$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02 Laufend'!$A$4:$N$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -654,17 +654,17 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Nora</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>N26 Debit</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>Karte bitte bestaetigen</t>
+          <t>Von Nora vorab beglichen</t>
         </is>
       </c>
     </row>
@@ -771,54 +771,54 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Unterkunft</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Quiver Tree Camping</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>vor Ort - bestaetigen</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="n">
+      <c r="F8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>Bargeld?</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="inlineStr">
-        <is>
-          <t>War nicht vorgebucht - Nacht vergangen</t>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>bar bezahlt - siehe Blatt 02</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Patrick</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Bargeld</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>720 NAD bar von Patrick gezahlt - Betrag steht in Blatt 02 Nr. 8 (keine Doppelzaehlung)</t>
         </is>
       </c>
     </row>
@@ -845,18 +845,18 @@
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>angezahlt (50%)</t>
+          <t>Deposit bezahlt - Rest siehe Blatt 02</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
         <v>24</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>Restzahlung vor Ort - Abreise 07.09.</t>
+          <t>Restzahlung 100.91 EUR am 05.09. an Klein Aus Vista Lodge - steht in Blatt 02 Nr. 11</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,11 @@
           <t>N26 Debit</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr"/>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Von Nora vorab beglichen</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1280,7 +1284,11 @@
           <t>N26 Debit</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr"/>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Von Nora vorab beglichen</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -1432,7 +1440,11 @@
           <t>N26 Debit</t>
         </is>
       </c>
-      <c r="L20" s="6" t="inlineStr"/>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>Von Nora vorab beglichen</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1480,7 +1492,11 @@
           <t>N26 Debit</t>
         </is>
       </c>
-      <c r="L21" s="6" t="inlineStr"/>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>Von Nora vorab beglichen</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n"/>
@@ -1532,7 +1548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2085,194 +2101,608 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Quiver Tree Forest</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Quivertree Forest Camping</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Unterkunft</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>720</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>NAD</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Patrick</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>Bargeld</t>
+        </is>
+      </c>
       <c r="M12" s="13">
         <f>IF(AND(H12&lt;&gt;"",J12&lt;&gt;"",J12&lt;&gt;0),H12/J12,"")</f>
         <v/>
       </c>
-      <c r="N12" s="6" t="n"/>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>Bar aus der Reisekasse; EUR zum ATM-Kurs 18.633 NAD/EUR umgerechnet</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Mariental</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Spar Mariental</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Lebensmittel</t>
+        </is>
+      </c>
       <c r="H13" s="12" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>N26 Debit</t>
+        </is>
+      </c>
       <c r="M13" s="13">
         <f>IF(AND(H13&lt;&gt;"",J13&lt;&gt;"",J13&lt;&gt;0),H13/J13,"")</f>
         <v/>
       </c>
-      <c r="N13" s="6" t="n"/>
+      <c r="N13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Keetmanshoop</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Agra Keetmanshoop - Fo</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Tanken</t>
+        </is>
+      </c>
       <c r="H14" s="12" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>N26 Debit</t>
+        </is>
+      </c>
       <c r="M14" s="13">
         <f>IF(AND(H14&lt;&gt;"",J14&lt;&gt;"",J14&lt;&gt;0),H14/J14,"")</f>
         <v/>
       </c>
-      <c r="N14" s="6" t="n"/>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>KATEGORIE ZU BESTAETIGEN - Agra ist Landhandel mit Tankstelle; N26 kategorisiert als Transport &amp; Auto</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Aus</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Klein Aus Vista Lodge</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Unterkunft</t>
+        </is>
+      </c>
       <c r="H15" s="12" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>100.91</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>N26 Debit</t>
+        </is>
+      </c>
       <c r="M15" s="13">
         <f>IF(AND(H15&lt;&gt;"",J15&lt;&gt;"",J15&lt;&gt;0),H15/J15,"")</f>
         <v/>
       </c>
-      <c r="N15" s="6" t="n"/>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>BETRAG PRUEFEN - Restzahlung Desert Horse Campsite (2 Naechte); geplant waren 48 EUR gesamt inkl. 24 EUR Deposit</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Kolmanskop</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Ghost Town Tours CC</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Aktivitäten</t>
+        </is>
+      </c>
       <c r="H16" s="12" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>N26 Debit</t>
+        </is>
+      </c>
       <c r="M16" s="13">
         <f>IF(AND(H16&lt;&gt;"",J16&lt;&gt;"",J16&lt;&gt;0),H16/J16,"")</f>
         <v/>
       </c>
-      <c r="N16" s="6" t="n"/>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>Geisterstadt-Tour Kolmanskop</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Aus</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Desert Deli</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
       <c r="H17" s="12" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="4" t="n"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>N26 Debit</t>
+        </is>
+      </c>
       <c r="M17" s="13">
         <f>IF(AND(H17&lt;&gt;"",J17&lt;&gt;"",J17&lt;&gt;0),H17/J17,"")</f>
         <v/>
       </c>
-      <c r="N17" s="6" t="n"/>
+      <c r="N17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Lüderitz</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Portugues Fisherman</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
       <c r="H18" s="12" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n"/>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>45.57</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>N26 Debit</t>
+        </is>
+      </c>
       <c r="M18" s="13">
         <f>IF(AND(H18&lt;&gt;"",J18&lt;&gt;"",J18&lt;&gt;0),H18/J18,"")</f>
         <v/>
       </c>
-      <c r="N18" s="6" t="n"/>
+      <c r="N18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Lüderitz</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Spar Lüderitz</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Lebensmittel</t>
+        </is>
+      </c>
       <c r="H19" s="12" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="n"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>N26 Debit</t>
+        </is>
+      </c>
       <c r="M19" s="13">
         <f>IF(AND(H19&lt;&gt;"",J19&lt;&gt;"",J19&lt;&gt;0),H19/J19,"")</f>
         <v/>
       </c>
-      <c r="N19" s="6" t="n"/>
+      <c r="N19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Lüderitz</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Studio88 Lüderitz</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
       <c r="H20" s="12" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>N26 Debit</t>
+        </is>
+      </c>
       <c r="M20" s="13">
         <f>IF(AND(H20&lt;&gt;"",J20&lt;&gt;"",J20&lt;&gt;0),H20/J20,"")</f>
         <v/>
       </c>
-      <c r="N20" s="6" t="n"/>
+      <c r="N20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Lüderitz</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Lüderitz Fuel Center</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Tanken</t>
+        </is>
+      </c>
       <c r="H21" s="12" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>N26 Debit</t>
+        </is>
+      </c>
       <c r="M21" s="13">
         <f>IF(AND(H21&lt;&gt;"",J21&lt;&gt;"",J21&lt;&gt;0),H21/J21,"")</f>
         <v/>
       </c>
-      <c r="N21" s="6" t="n"/>
+      <c r="N21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n"/>
@@ -3225,44 +3655,234 @@
       <c r="N71" s="6" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="10" t="n"/>
-      <c r="B72" s="10" t="n"/>
-      <c r="C72" s="10" t="n"/>
-      <c r="D72" s="10" t="n"/>
-      <c r="E72" s="10" t="n"/>
-      <c r="F72" s="10" t="inlineStr">
+      <c r="A72" s="4" t="n"/>
+      <c r="B72" s="4" t="n"/>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="n"/>
+      <c r="G72" s="4" t="n"/>
+      <c r="H72" s="12" t="n"/>
+      <c r="I72" s="4" t="n"/>
+      <c r="J72" s="5" t="n"/>
+      <c r="K72" s="4" t="n"/>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="13">
+        <f>IF(AND(H72&lt;&gt;"",J72&lt;&gt;"",J72&lt;&gt;0),H72/J72,"")</f>
+        <v/>
+      </c>
+      <c r="N72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n"/>
+      <c r="B73" s="4" t="n"/>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="4" t="n"/>
+      <c r="E73" s="4" t="n"/>
+      <c r="F73" s="4" t="n"/>
+      <c r="G73" s="4" t="n"/>
+      <c r="H73" s="12" t="n"/>
+      <c r="I73" s="4" t="n"/>
+      <c r="J73" s="5" t="n"/>
+      <c r="K73" s="4" t="n"/>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="13">
+        <f>IF(AND(H73&lt;&gt;"",J73&lt;&gt;"",J73&lt;&gt;0),H73/J73,"")</f>
+        <v/>
+      </c>
+      <c r="N73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n"/>
+      <c r="B74" s="4" t="n"/>
+      <c r="C74" s="4" t="n"/>
+      <c r="D74" s="4" t="n"/>
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="n"/>
+      <c r="G74" s="4" t="n"/>
+      <c r="H74" s="12" t="n"/>
+      <c r="I74" s="4" t="n"/>
+      <c r="J74" s="5" t="n"/>
+      <c r="K74" s="4" t="n"/>
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="13">
+        <f>IF(AND(H74&lt;&gt;"",J74&lt;&gt;"",J74&lt;&gt;0),H74/J74,"")</f>
+        <v/>
+      </c>
+      <c r="N74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n"/>
+      <c r="B75" s="4" t="n"/>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="12" t="n"/>
+      <c r="I75" s="4" t="n"/>
+      <c r="J75" s="5" t="n"/>
+      <c r="K75" s="4" t="n"/>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="13">
+        <f>IF(AND(H75&lt;&gt;"",J75&lt;&gt;"",J75&lt;&gt;0),H75/J75,"")</f>
+        <v/>
+      </c>
+      <c r="N75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n"/>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="12" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="J76" s="5" t="n"/>
+      <c r="K76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="13">
+        <f>IF(AND(H76&lt;&gt;"",J76&lt;&gt;"",J76&lt;&gt;0),H76/J76,"")</f>
+        <v/>
+      </c>
+      <c r="N76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n"/>
+      <c r="B77" s="4" t="n"/>
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="4" t="n"/>
+      <c r="E77" s="4" t="n"/>
+      <c r="F77" s="4" t="n"/>
+      <c r="G77" s="4" t="n"/>
+      <c r="H77" s="12" t="n"/>
+      <c r="I77" s="4" t="n"/>
+      <c r="J77" s="5" t="n"/>
+      <c r="K77" s="4" t="n"/>
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="13">
+        <f>IF(AND(H77&lt;&gt;"",J77&lt;&gt;"",J77&lt;&gt;0),H77/J77,"")</f>
+        <v/>
+      </c>
+      <c r="N77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n"/>
+      <c r="B78" s="4" t="n"/>
+      <c r="C78" s="4" t="n"/>
+      <c r="D78" s="4" t="n"/>
+      <c r="E78" s="4" t="n"/>
+      <c r="F78" s="4" t="n"/>
+      <c r="G78" s="4" t="n"/>
+      <c r="H78" s="12" t="n"/>
+      <c r="I78" s="4" t="n"/>
+      <c r="J78" s="5" t="n"/>
+      <c r="K78" s="4" t="n"/>
+      <c r="L78" s="4" t="n"/>
+      <c r="M78" s="13">
+        <f>IF(AND(H78&lt;&gt;"",J78&lt;&gt;"",J78&lt;&gt;0),H78/J78,"")</f>
+        <v/>
+      </c>
+      <c r="N78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n"/>
+      <c r="B79" s="4" t="n"/>
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="4" t="n"/>
+      <c r="E79" s="4" t="n"/>
+      <c r="F79" s="4" t="n"/>
+      <c r="G79" s="4" t="n"/>
+      <c r="H79" s="12" t="n"/>
+      <c r="I79" s="4" t="n"/>
+      <c r="J79" s="5" t="n"/>
+      <c r="K79" s="4" t="n"/>
+      <c r="L79" s="4" t="n"/>
+      <c r="M79" s="13">
+        <f>IF(AND(H79&lt;&gt;"",J79&lt;&gt;"",J79&lt;&gt;0),H79/J79,"")</f>
+        <v/>
+      </c>
+      <c r="N79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n"/>
+      <c r="B80" s="4" t="n"/>
+      <c r="C80" s="4" t="n"/>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="n"/>
+      <c r="G80" s="4" t="n"/>
+      <c r="H80" s="12" t="n"/>
+      <c r="I80" s="4" t="n"/>
+      <c r="J80" s="5" t="n"/>
+      <c r="K80" s="4" t="n"/>
+      <c r="L80" s="4" t="n"/>
+      <c r="M80" s="13">
+        <f>IF(AND(H80&lt;&gt;"",J80&lt;&gt;"",J80&lt;&gt;0),H80/J80,"")</f>
+        <v/>
+      </c>
+      <c r="N80" s="6" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n"/>
+      <c r="B81" s="4" t="n"/>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="n"/>
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="n"/>
+      <c r="G81" s="4" t="n"/>
+      <c r="H81" s="12" t="n"/>
+      <c r="I81" s="4" t="n"/>
+      <c r="J81" s="5" t="n"/>
+      <c r="K81" s="4" t="n"/>
+      <c r="L81" s="4" t="n"/>
+      <c r="M81" s="13">
+        <f>IF(AND(H81&lt;&gt;"",J81&lt;&gt;"",J81&lt;&gt;0),H81/J81,"")</f>
+        <v/>
+      </c>
+      <c r="N81" s="6" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="n"/>
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="10" t="n"/>
+      <c r="E82" s="10" t="n"/>
+      <c r="F82" s="10" t="inlineStr">
         <is>
           <t>SUMME echte Ausgaben (Typ = Ausgabe)</t>
         </is>
       </c>
-      <c r="G72" s="10" t="n"/>
-      <c r="H72" s="10" t="n"/>
-      <c r="I72" s="10" t="n"/>
-      <c r="J72" s="11">
-        <f>SUMIFS(J5:J71,D5:D71,"Ausgabe")</f>
-        <v/>
-      </c>
-      <c r="K72" s="10" t="n"/>
-      <c r="L72" s="10" t="n"/>
-      <c r="M72" s="10" t="n"/>
-      <c r="N72" s="10" t="n"/>
+      <c r="G82" s="10" t="n"/>
+      <c r="H82" s="10" t="n"/>
+      <c r="I82" s="10" t="n"/>
+      <c r="J82" s="11">
+        <f>SUMIFS(J5:J81,D5:D81,"Ausgabe")</f>
+        <v/>
+      </c>
+      <c r="K82" s="10" t="n"/>
+      <c r="L82" s="10" t="n"/>
+      <c r="M82" s="10" t="n"/>
+      <c r="N82" s="10" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N71"/>
+  <autoFilter ref="A4:N81"/>
   <dataValidations count="5">
-    <dataValidation sqref="D5:D71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Ausgabe,Abhebung,Transfer"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Flug,Mietwagen,Unterkunft,Tanken,Lebensmittel,Restaurant,Eintritt,Aktivitäten,Ausrüstung,Gebühren,Shopping,Sonstiges,Bargeld"</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NAD,EUR,ZAR"</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K5:K81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Patrick,Nora,Kasse,TBD"</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Oberbank Debit,Mastercard card complete,N26 Debit,Bargeld,Ueberweisung,TBD"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3350,7 +3970,7 @@
         <v/>
       </c>
       <c r="C7" s="19">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!G5:G71,A7,'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!G5:G81,A7,'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
       <c r="D7" s="19">
@@ -3369,7 +3989,7 @@
         <v/>
       </c>
       <c r="C8" s="19">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!G5:G71,A8,'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!G5:G81,A8,'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
       <c r="D8" s="19">
@@ -3388,7 +4008,7 @@
         <v/>
       </c>
       <c r="C9" s="19">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!G5:G71,A9,'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!G5:G81,A9,'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
       <c r="D9" s="19">
@@ -3407,7 +4027,7 @@
         <v/>
       </c>
       <c r="C10" s="19">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!G5:G71,A10,'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!G5:G81,A10,'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
       <c r="D10" s="19">
@@ -3426,7 +4046,7 @@
         <v/>
       </c>
       <c r="C11" s="19">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!G5:G71,A11,'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!G5:G81,A11,'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
       <c r="D11" s="19">
@@ -3445,7 +4065,7 @@
         <v/>
       </c>
       <c r="C12" s="19">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!G5:G71,A12,'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!G5:G81,A12,'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
       <c r="D12" s="19">
@@ -3464,7 +4084,7 @@
         <v/>
       </c>
       <c r="C13" s="19">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!G5:G71,A13,'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!G5:G81,A13,'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
       <c r="D13" s="19">
@@ -3483,7 +4103,7 @@
         <v/>
       </c>
       <c r="C14" s="19">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!G5:G71,A14,'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!G5:G81,A14,'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
       <c r="D14" s="19">
@@ -3502,7 +4122,7 @@
         <v/>
       </c>
       <c r="C15" s="19">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!G5:G71,A15,'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!G5:G81,A15,'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
       <c r="D15" s="19">
@@ -3521,7 +4141,7 @@
         <v/>
       </c>
       <c r="C16" s="19">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!G5:G71,A16,'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!G5:G81,A16,'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
       <c r="D16" s="19">
@@ -3540,7 +4160,7 @@
         <v/>
       </c>
       <c r="C17" s="19">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!G5:G71,A17,'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!G5:G81,A17,'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
       <c r="D17" s="19">
@@ -3559,7 +4179,7 @@
         <v/>
       </c>
       <c r="C18" s="19">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!G5:G71,A18,'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!G5:G81,A18,'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
       <c r="D18" s="19">
@@ -3658,7 +4278,7 @@
         </is>
       </c>
       <c r="C29" s="21">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!K5:K71,"Patrick",'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!K5:K81,"Patrick",'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
     </row>
@@ -3680,7 +4300,7 @@
         </is>
       </c>
       <c r="C31" s="21">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!K5:K71,"Nora",'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!K5:K81,"Nora",'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
     </row>
@@ -3691,7 +4311,7 @@
         </is>
       </c>
       <c r="C32" s="21">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!K5:K71,"Kasse",'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!K5:K81,"Kasse",'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3707,7 +4327,7 @@
         </is>
       </c>
       <c r="C33" s="21">
-        <f>SUMIF('01 Bezahlt'!J5:J21,"TBD",'01 Bezahlt'!H5:H21)+SUMIFS('02 Laufend'!J5:J71,'01 Bezahlt'!J5:J21,"TBD",'02 Laufend'!D5:D71,"Ausgabe")</f>
+        <f>SUMIF('01 Bezahlt'!J5:J21,"TBD",'01 Bezahlt'!H5:H21)+SUMIFS('02 Laufend'!J5:J81,'01 Bezahlt'!J5:J21,"TBD",'02 Laufend'!D5:D81,"Ausgabe")</f>
         <v/>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3739,7 +4359,7 @@
         </is>
       </c>
       <c r="C37" s="21">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!D5:D71,"Abhebung")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!D5:D81,"Abhebung")</f>
         <v/>
       </c>
     </row>
@@ -3750,7 +4370,7 @@
         </is>
       </c>
       <c r="C38" s="21">
-        <f>SUMIFS('02 Laufend'!J5:J71,'02 Laufend'!D5:D71,"Ausgabe",'02 Laufend'!L5:L71,"Bargeld")</f>
+        <f>SUMIFS('02 Laufend'!J5:J81,'02 Laufend'!D5:D81,"Ausgabe",'02 Laufend'!L5:L81,"Bargeld")</f>
         <v/>
       </c>
     </row>
@@ -3800,7 +4420,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Vorschuss / Ausgleich Reisekasse</t>
+          <t>Ausgleich fuer Noras Vorauszahlungen (Flug + Unterkuenfte)</t>
         </is>
       </c>
     </row>
